--- a/docs/strategy/ROADMAP_WORKBOOK.xlsx
+++ b/docs/strategy/ROADMAP_WORKBOOK.xlsx
@@ -10,6 +10,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phases" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checklist Mirror" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Current Priorities" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weekly Focus" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -423,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -462,7 +464,7 @@
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -583,6 +585,82 @@
       <c r="B17" s="1" t="inlineStr">
         <is>
           <t>Stuur nu vooral op revenue + proof, deliverystabiliteit, lifecycle, operating rhythm en selectieve SaaS-readiness.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="1" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Current Focus</t>
+        </is>
+      </c>
+      <c r="B19" s="1" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr"/>
+      <c r="B20" s="1" t="inlineStr">
+        <is>
+          <t>Website redesign afronden</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr"/>
+      <c r="B21" s="1" t="inlineStr">
+        <is>
+          <t>Dashboard redesign afronden</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr"/>
+      <c r="B22" s="1" t="inlineStr">
+        <is>
+          <t>Voorbereiding productverbreding decision-complete houden</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr"/>
+      <c r="B23" s="1" t="inlineStr">
+        <is>
+          <t>Next 30d: Commercial rhythm hardening</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr"/>
+      <c r="B24" s="1" t="inlineStr">
+        <is>
+          <t>Next 30d: Governance execution</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr"/>
+      <c r="B25" s="1" t="inlineStr">
+        <is>
+          <t>Next 30d: Delivery control</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr"/>
+      <c r="B26" s="1" t="inlineStr">
+        <is>
+          <t>Next 30d: Source-of-truth hardening</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr"/>
+      <c r="B27" s="1" t="inlineStr">
+        <is>
+          <t>Next 30d: Secrets and security hygiene</t>
         </is>
       </c>
     </row>
@@ -2333,4 +2411,685 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Horizon</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Why now</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Status / guardrail</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Active now</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Website redesign afronden</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>Publieke commerciële laag moet kloppen, maar zonder nieuwe scopegroei.</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>Claude / Founder</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Active now</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>Dashboard redesign afronden</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>Dashboard moet managementgebruik en decision support zichtbaar verbeteren.</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
+          <t>Codex / Founder</t>
+        </is>
+      </c>
+      <c r="E3" s="1" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Active now</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>Voorbereiding productverbreding decision-complete houden</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>Wel voorbereiden, nog niet breed bouwen voordat de operating core harder staat.</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>Codex / Founder</t>
+        </is>
+      </c>
+      <c r="E4" s="1" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>Next 30 days</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>Commercial rhythm hardening</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>Pipeline moet van geheugen naar echt ritme bewegen.</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="E5" s="1" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>Next 30 days</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>Governance execution</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t>Scorecard, maandreview en capacity map moeten echt gebruikt worden.</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="E6" s="1" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Next 30 days</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>Delivery control</t>
+        </is>
+      </c>
+      <c r="C7" s="1" t="inlineStr">
+        <is>
+          <t>Actieve trajecten moeten checkpoint- en risicozichtbaarheid krijgen.</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="E7" s="1" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Next 30 days</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="inlineStr">
+        <is>
+          <t>Source-of-truth hardening</t>
+        </is>
+      </c>
+      <c r="C8" s="1" t="inlineStr">
+        <is>
+          <t>Repo, CRM, workbook en Docs_External mogen niet opnieuw concurreren.</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="E8" s="1" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>Next 30 days</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="inlineStr">
+        <is>
+          <t>Secrets and security hygiene</t>
+        </is>
+      </c>
+      <c r="C9" s="1" t="inlineStr">
+        <is>
+          <t>Lokale sleutel- en logsporen moeten netjes en veilig worden gemaakt.</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="E9" s="1" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>30-60 days</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t>Proof capture hardening</t>
+        </is>
+      </c>
+      <c r="C10" s="1" t="inlineStr">
+        <is>
+          <t>Bewijsopbouw moet in het kernritme landen, niet achteraf.</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="inlineStr">
+        <is>
+          <t>Founder + sales</t>
+        </is>
+      </c>
+      <c r="E10" s="1" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>30-60 days</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="inlineStr">
+        <is>
+          <t>Throughput metrics</t>
+        </is>
+      </c>
+      <c r="C11" s="1" t="inlineStr">
+        <is>
+          <t>Cycle time, defects en volume moeten zichtbaar worden voor echte sturing.</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="inlineStr">
+        <is>
+          <t>Founder + ops</t>
+        </is>
+      </c>
+      <c r="E11" s="1" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>30-60 days</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="inlineStr">
+        <is>
+          <t>Delegated run</t>
+        </is>
+      </c>
+      <c r="C12" s="1" t="inlineStr">
+        <is>
+          <t>Overdraagbaarheid moet getest worden in plaats van verondersteld.</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="inlineStr">
+        <is>
+          <t>Founder + future operator</t>
+        </is>
+      </c>
+      <c r="E12" s="1" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>30-60 days</t>
+        </is>
+      </c>
+      <c r="B13" s="1" t="inlineStr">
+        <is>
+          <t>Founder dependency reduction</t>
+        </is>
+      </c>
+      <c r="C13" s="1" t="inlineStr">
+        <is>
+          <t>De centrale triage- en herstelrol moet explicieter en kleiner worden.</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="E13" s="1" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>60-90 days</t>
+        </is>
+      </c>
+      <c r="B14" s="1" t="inlineStr">
+        <is>
+          <t>Selective tooling shortlist</t>
+        </is>
+      </c>
+      <c r="C14" s="1" t="inlineStr">
+        <is>
+          <t>Alleen bewezen frictie mag leiden tot toolingverdieping.</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="inlineStr">
+        <is>
+          <t>Founder + ops/product</t>
+        </is>
+      </c>
+      <c r="E14" s="1" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>60-90 days</t>
+        </is>
+      </c>
+      <c r="B15" s="1" t="inlineStr">
+        <is>
+          <t>Operator model decision</t>
+        </is>
+      </c>
+      <c r="C15" s="1" t="inlineStr">
+        <is>
+          <t>Bepalen of een vaste ops-/delivery-owner logisch wordt.</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="E15" s="1" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>60-90 days</t>
+        </is>
+      </c>
+      <c r="B16" s="1" t="inlineStr">
+        <is>
+          <t>Automation guardrails</t>
+        </is>
+      </c>
+      <c r="C16" s="1" t="inlineStr">
+        <is>
+          <t>Automation pas starten na ritme, owners en metrics.</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="inlineStr">
+        <is>
+          <t>Founder + product</t>
+        </is>
+      </c>
+      <c r="E16" s="1" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="1" t="n"/>
+      <c r="C17" s="1" t="n"/>
+      <c r="D17" s="1" t="n"/>
+      <c r="E17" s="1" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>Not now</t>
+        </is>
+      </c>
+      <c r="B18" s="1" t="inlineStr">
+        <is>
+          <t>Guardrail</t>
+        </is>
+      </c>
+      <c r="C18" s="1" t="inlineStr"/>
+      <c r="D18" s="1" t="inlineStr"/>
+      <c r="E18" s="1" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Not now</t>
+        </is>
+      </c>
+      <c r="B19" s="1" t="inlineStr">
+        <is>
+          <t>Geen nieuw contentproject als hoofdlijn</t>
+        </is>
+      </c>
+      <c r="C19" s="1" t="inlineStr"/>
+      <c r="D19" s="1" t="inlineStr"/>
+      <c r="E19" s="1" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Not now</t>
+        </is>
+      </c>
+      <c r="B20" s="1" t="inlineStr">
+        <is>
+          <t>Geen Stripe- of billingproject</t>
+        </is>
+      </c>
+      <c r="C20" s="1" t="inlineStr"/>
+      <c r="D20" s="1" t="inlineStr"/>
+      <c r="E20" s="1" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>Not now</t>
+        </is>
+      </c>
+      <c r="B21" s="1" t="inlineStr">
+        <is>
+          <t>Geen brede automationlaag</t>
+        </is>
+      </c>
+      <c r="C21" s="1" t="inlineStr"/>
+      <c r="D21" s="1" t="inlineStr"/>
+      <c r="E21" s="1" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Not now</t>
+        </is>
+      </c>
+      <c r="B22" s="1" t="inlineStr">
+        <is>
+          <t>Geen self-service onboarding push</t>
+        </is>
+      </c>
+      <c r="C22" s="1" t="inlineStr"/>
+      <c r="D22" s="1" t="inlineStr"/>
+      <c r="E22" s="1" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>Not now</t>
+        </is>
+      </c>
+      <c r="B23" s="1" t="inlineStr">
+        <is>
+          <t>Geen brede nieuwe productimplementaties buiten de voorbereidingslaag</t>
+        </is>
+      </c>
+      <c r="C23" s="1" t="inlineStr"/>
+      <c r="D23" s="1" t="inlineStr"/>
+      <c r="E23" s="1" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Prompt</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Week van</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr"/>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>Kies de week die nu loopt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Deze week telt vooral</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr"/>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>Welke ene beweging maakt deze week succesvol?</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Belangrijkste commerciële push</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr"/>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>Welk gesprek, voorstel of batch moet deze week echt bewegen?</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>Belangrijkste delivery-risk</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr"/>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>Welk klanttraject vraagt nu de meeste aandacht?</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>Topprioriteit 1</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>Website redesign afronden</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t>Houd dit concreet en uitvoerbaar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Topprioriteit 2</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>Commercial rhythm hardening</t>
+        </is>
+      </c>
+      <c r="C7" s="1" t="inlineStr">
+        <is>
+          <t>Kies een echte fix, geen abstract thema.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Topprioriteit 3</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="inlineStr">
+        <is>
+          <t>Governance execution</t>
+        </is>
+      </c>
+      <c r="C8" s="1" t="inlineStr">
+        <is>
+          <t>Alleen invullen als je het deze week echt doet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>Niet doen 1</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="inlineStr"/>
+      <c r="C9" s="1" t="inlineStr">
+        <is>
+          <t>Wat laat je deze week bewust liggen?</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Niet doen 2</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="inlineStr"/>
+      <c r="C10" s="1" t="inlineStr">
+        <is>
+          <t>Wat laat je deze week bewust liggen?</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>Niet doen 3</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="inlineStr"/>
+      <c r="C11" s="1" t="inlineStr">
+        <is>
+          <t>Wat laat je deze week bewust liggen?</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Besluit deze week</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="inlineStr"/>
+      <c r="C12" s="1" t="inlineStr">
+        <is>
+          <t>Welk besluit moet expliciet in de decision log landen?</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>